--- a/important_mails_2026-04-20.xlsx
+++ b/important_mails_2026-04-20.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H138"/>
+  <dimension ref="A1:H141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -500,21 +500,187 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
+          <t>Mon, 20 Apr 2026 14:16:35 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+          <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Dein Einkaufswagen wartet</t>
+          <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
+ A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Do not reply back to this e-mail!
+Hello,
+Thank you for submitting a document to the Chemical Safety Compliance Team.
+● The document uploaded for "B0DD7R3PPG" is incomplete, inaccurate or otherwise conflicting, and cannot be used for classification. Specifically:
+→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
+The SDS does not include the legislation/regulation in accordance with the document was created
+Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
+For guidance on Safety Data Sheet requirements, please refer to https://sellercentral.amazon.com/help/hub/reference/G5G6BBSA6FZQP9CP
+Once you have corrected the problems listed above, please re-upload a valid document in Account Health Dashboard under "Regulatory Compliance" section. For any questions/appeals regarding these product/other products, please submit them ( for each ASIN separately ) in "Account Health Dashboard" under the relevant Appeal reason:
+1. Go to the Account Health page and select the Regulatory Compliance tab
+2. Choose next steps.
+3. Click Submit button for the product y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 20 Apr 2026 09:57:17 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
+ DOC REVIEW</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Do not reply back to this e-mail!
+Hello,
+Thank you for submitting a document to the Chemical Safety Compliance Team.
+● The document uploaded for "B0FCDRNTT8x`" is incomplete, inaccurate or otherwise conflicting, and cannot be used for classification. Specifically:
+→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
+The SDS does not include the legislation/regulation in accordance with the document was created
+Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
+For guidance on Safety Data Sheet requirements, please refer to https://sellercentral.amazon.com/help/hub/reference/G5G6BBSA6FZQP9CP
+Once you have corrected the problems listed above, please re-upload a valid document in Account Health Dashboard under "Regulatory Compliance" section. For any questions/appeals regarding these product/other products, please submit them ( for each ASIN separately ) in "Account Health Dashboard" under the relevant Appeal reason:
+1. Go to the Account Health page and select the Regulatory Compliance tab
+2. Choose next steps.
+3. Click Submit button for the product</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 20 Apr 2026 16:06:35 +0800 (GMT+08:00)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon DV TIC</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>尊敬的卖家，您好。
+我们可以为您提供亚马逊DV验证报告服务。
+验证费用：
+【玩具】500元（RMB）/ASIN；
+【电动自行车用充电器及电池】4500元（RMB）/ASIN；
+【移动电源及便携式电源产品】5000元（RMB）/ASIN。
+如涉及较多ASIN或有其他需求，我们将根据具体情况提供优惠报价。
+商品测试：
+如您的商品需额外进行合规测试，请提供实物图片和商品参数以及销售国家等，以便评估测试费用。
+服务流程如下：
+登录卖家中心 “合规管理”（MYC）；
+针对待处理 ASIN，选择 “CVC威凯” 提交验证申请；
+提供所需资料：申请表、测试报告、产品六面实物照片（非包装图）、标签警示语、用户手册/使用说明书等；
+CVC威凯将进行检测或合规验证，并将结果直接提交亚马逊；如需整改，我们会及时与您沟通。
+如需进一步了解或希望直接安排服务，可直接通过以下方式联系我，我们将全程协助您完成验证流程。
+您也可联系官方邮箱专员咨询：amazondv@cei1958.com
+感谢您的支持，期待与您合作！
+如您已经对接我司业务员，请忽略此信息，不便之处敬请谅解。
+Dear Seller,
+Greetings.
+We are pleased to offer Amazon DV Verification Report services to support your compliance needs.
+Verification Fee:
+【Toys】¥500 (RMB) per ASIN.
+【E-bikes lithium-ion batteries and chargers】¥4500 (RMB) per ASIN.
+【Power Bank and Portable Power Station】¥5000 (RMB) per ASIN.
+If you have multiple ASINs or special requirements, we can provide a customized discounted quote based on your situation.
+Product Testing:If your product requires additional compliance testing, please provide physical product photos, specify the target sales country/region and product parameter so we can assess the testing fees accordingly.
+Service Process:
+Log in to your Seller Central and navigate to “Compliance Managemen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Dein Einkaufswagen wartet</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -535,39 +701,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $44.85 in an attempt to settle your Amazon seller account balance.
@@ -583,39 +749,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -635,39 +801,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -683,39 +849,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -735,39 +901,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -784,39 +950,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -828,39 +994,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -883,39 +1049,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -930,39 +1096,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 03:38:27 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -978,39 +1144,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
@@ -1034,39 +1200,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -1085,39 +1251,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -1133,39 +1299,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK
 [Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
@@ -1177,39 +1343,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -1229,39 +1395,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -1276,39 +1442,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Verify your primary operating address for tax purposes</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  Verify your primary operating address for tax purposes
@@ -1325,39 +1491,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1371,39 +1537,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -1422,40 +1588,40 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -1469,39 +1635,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1523,39 +1689,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1578,39 +1744,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1631,39 +1797,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1686,39 +1852,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -1727,39 +1893,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -1775,39 +1941,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1833,39 +1999,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1886,39 +2052,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1944,39 +2110,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1996,40 +2162,40 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -2045,39 +2211,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2097,39 +2263,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2155,39 +2321,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2203,39 +2369,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2256,39 +2422,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2312,39 +2478,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
@@ -2359,39 +2525,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2405,40 +2571,40 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -2455,39 +2621,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2507,39 +2673,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2556,39 +2722,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -2611,39 +2777,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2663,39 +2829,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -2712,39 +2878,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2762,40 +2928,40 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 15:28:03 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -2813,39 +2979,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 12:03:53 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -2865,39 +3031,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -2918,39 +3084,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -2971,40 +3137,40 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>VAT Calculation Services will calculate VAT by shipment as of June
  1</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
  New tax calculation method ensures compliance with European e-invoicing mandates.
@@ -3020,39 +3186,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -3075,39 +3241,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3125,39 +3291,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3175,39 +3341,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3227,39 +3393,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3277,39 +3443,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3327,39 +3493,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3377,39 +3543,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -3424,39 +3590,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3474,39 +3640,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3524,39 +3690,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3574,39 +3740,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3621,39 +3787,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3668,39 +3834,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3715,39 +3881,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3766,40 +3932,40 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -3818,39 +3984,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -3860,39 +4026,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3910,39 +4076,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -3958,40 +4124,40 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -4009,39 +4175,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -4074,39 +4240,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Store inventory at origin in China with lower costs and faster speeds.
@@ -4121,39 +4287,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4172,39 +4338,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -4223,39 +4389,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
@@ -4267,39 +4433,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
@@ -4315,39 +4481,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -4359,39 +4525,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4406,39 +4572,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4450,39 +4616,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4494,39 +4660,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4538,39 +4704,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4582,39 +4748,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4626,39 +4792,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4670,39 +4836,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4714,39 +4880,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4758,39 +4924,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4802,39 +4968,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4853,39 +5019,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4897,39 +5063,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4941,39 +5107,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4985,39 +5151,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5029,39 +5195,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5073,39 +5239,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -5117,39 +5283,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5161,39 +5327,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5212,39 +5378,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5256,40 +5422,40 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5308,39 +5474,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5352,39 +5518,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -5403,39 +5569,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -5467,39 +5633,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -5526,39 +5692,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -5570,39 +5736,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -5612,39 +5778,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -5654,39 +5820,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -5716,39 +5882,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -5766,39 +5932,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -5815,39 +5981,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -5863,39 +6029,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -5924,39 +6090,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -5977,39 +6143,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6024,39 +6190,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -6070,40 +6236,40 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -6119,39 +6285,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -6167,39 +6333,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -6215,39 +6381,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -6263,40 +6429,40 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -6312,39 +6478,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6362,39 +6528,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -6410,39 +6576,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6457,39 +6623,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -6504,39 +6670,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -6557,40 +6723,40 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -6605,39 +6771,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -6658,39 +6824,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -6723,39 +6889,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -6768,39 +6934,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6821,39 +6987,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6876,39 +7042,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -6924,39 +7090,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -6976,39 +7142,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -7027,39 +7193,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -7068,39 +7234,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -7118,39 +7284,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -7180,39 +7346,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7228,39 +7394,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.

--- a/important_mails_2026-04-20.xlsx
+++ b/important_mails_2026-04-20.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,22 +500,72 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>Mon, 20 Apr 2026 21:09:24 +0000</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai US,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>Mon, 20 Apr 2026 14:16:35 +0000</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -532,40 +582,40 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 09:57:17 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -582,39 +632,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 16:06:35 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Amazon DV TIC</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，您好。
 我们可以为您提供亚马逊DV验证报告服务。
@@ -648,39 +698,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -701,39 +751,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $44.85 in an attempt to settle your Amazon seller account balance.
@@ -749,39 +799,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -801,39 +851,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -849,39 +899,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -901,39 +951,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -950,54 +1000,10 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Cher vendeur,
- Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
- Le montant débité sur votre carte bancaire peut être inférieur au montant total impayé si vous disposez d'une limite de crédit imposée par votre banque. Nous continuerons d'essayer de débiter votre carte bancaire toutes les 24 heures jusqu'à ce que le solde restant de votre compte soit entièrement payé.
- Vous pouvez également utiliser la fonction Effectuer un paiement pour régler le solde. Pour en savoir plus, recherchez « Effectuer un paiement » dans l'Aide de Seller Central.
- Vous pouvez consulter votre solde à tout moment en vous connectant à la section Rapport sur les paiements de votre compte.
- Merci de vendre sur Amazon.
-Amazon Payments Europe SCA (société en commandite par actions) est immatriculée au Registre de Commerce et des Sociétés de Luxembourg (n° 153 265) et sise 38, avenue John F. Kennedy, L-1855 Luxembourg. Numéro de TVA : LU 24448288. Amazon Payments Europe SCA est autorisée par la Commission de Surveillance du Secteur Financier en tant qu’établissement de monnaie électronique (licence n° 36/10). Ama</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1012,76 +1018,21 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
+          <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
+          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Negative balance adjustment across your Selling on Amazon accounts</t>
+          <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- We’ve adjusted your negative balance of €261.54 that was due from your Amazon.fr seller account on April 13, 2026, with funds that were available in your Amazon.be, Amazon.es, Amazon.nl accounts. You can view your account balance at any time by logging into your account and navigating to the Payments dashboard .
-For more information, go to Negative balance adjustment across your accounts .
-Regards,
-Amazon Payments Europe
- Report an issue with this email
- If you have any questions, visit: Seller Central
- To change your email preferences, visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon Payments Europe
- 38 avenue John F. Kennedy,
- L-1855 Luxembourg, Registered in Luxembourg No. B-101818,
- Share Capital 165.833 EUR,
- Business License Number: 134248,
- Luxembourg VAT Reg. No. LU 20260743.
- This email is sent from an unmonitored email address.
- SPC-EUAmazon-439806292595808</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Action Required: Website Suppressed ASINs</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -1096,39 +1047,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 03:38:27 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -1144,39 +1095,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
@@ -1200,39 +1151,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -1251,39 +1202,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -1299,39 +1250,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK
 [Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
@@ -1343,39 +1294,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -1395,39 +1346,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -1442,39 +1393,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Verify your primary operating address for tax purposes</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  Verify your primary operating address for tax purposes
@@ -1491,39 +1442,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1537,39 +1488,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -1588,40 +1539,40 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -1635,39 +1586,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1689,39 +1640,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1744,39 +1695,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1797,39 +1748,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1852,39 +1803,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -1893,39 +1844,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -1941,39 +1892,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1999,39 +1950,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2052,39 +2003,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2110,39 +2061,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2162,40 +2113,40 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -2211,39 +2162,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2263,39 +2214,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2321,39 +2272,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2369,10 +2320,54 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Cher vendeur,
+ Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
+ Le montant débité sur votre carte bancaire peut être inférieur au montant total impayé si vous disposez d'une limite de crédit imposée par votre banque. Nous continuerons d'essayer de débiter votre carte bancaire toutes les 24 heures jusqu'à ce que le solde restant de votre compte soit entièrement payé.
+ Vous pouvez également utiliser la fonction Effectuer un paiement pour régler le solde. Pour en savoir plus, recherchez « Effectuer un paiement » dans l'Aide de Seller Central.
+ Vous pouvez consulter votre solde à tout moment en vous connectant à la section Rapport sur les paiements de votre compte.
+ Merci de vendre sur Amazon.
+Amazon Payments Europe SCA (société en commandite par actions) est immatriculée au Registre de Commerce et des Sociétés de Luxembourg (n° 153 265) et sise 38, avenue John F. Kennedy, L-1855 Luxembourg. Numéro de TVA : LU 24448288. Amazon Payments Europe SCA est autorisée par la Commission de Surveillance du Secteur Financier en tant qu’établissement de monnaie électronique (licence n° 36/10). Ama</t>
+        </is>
+      </c>
+    </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2387,38 +2382,40 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
+          <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
+          <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
- Hello Weihai US,
-The following automated unfulfillable FBA removal orders have been created based on your automated settings.
- Removal order ID pVfzD86piw
- You can view the removals on Removal Order Details in your seller account by using the Search tool.
-The next removal order will be created as scheduled on April 5, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
-To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
- Thank you.
-The Fulfillment by Amazon team
-Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+This title will display on mobile devices
+ We’ve adjusted your negative balance of €261.54 that was due from your Amazon.fr seller account on April 13, 2026, with funds that were available in your Amazon.be, Amazon.es, Amazon.nl accounts. You can view your account balance at any time by logging into your account and navigating to the Payments dashboard .
+For more information, go to Negative balance adjustment across your accounts .
+Regards,
+Amazon Payments Europe
  Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
+ If you have any questions, visit: Seller Central
+ To change your email preferences, visit: Notification Preferences
  Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-USAmazon-1213863031250684</t>
+ Amazon Payments Europe
+ 38 avenue John F. Kennedy,
+ L-1855 Luxembourg, Registered in Luxembourg No. B-101818,
+ Share Capital 165.833 EUR,
+ Business License Number: 134248,
+ Luxembourg VAT Reg. No. LU 20260743.
+ This email is sent from an unmonitored email address.
+ SPC-EUAmazon-439806292595808</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4076,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4094,70 +4091,22 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
+          <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Action Required: Website Suppressed ASINs</t>
+          <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
+ Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
-We recommend you to submit the required documents to un-suppress your ASIN and activate your listings.
-Here is a sample of your suppressed ASINs:
-B0F13M1H6F, B0D97JS8WD
-You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
-https://sellercentral.amazon.ca/fixyourproducts/drafts
-To upload the required documents or to appeal in-order to un-suppress the ASINs, please follow this path  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
- https://sellercentral.amazon.ca/performance/account/health/compliance-request
-If you need further help, please raise a case via contact us. - https://sellercentral.amazon.ca/cu/contact-us?ref=xx_ContactUs_xxxx_helphub
-If you are not the correct point of contact, please re-direct this email to the correct point of contact</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
- Reglamento relativo a la seguridad general de los productos</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -4175,39 +4124,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -4240,39 +4189,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Store inventory at origin in China with lower costs and faster speeds.
@@ -4287,39 +4236,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4338,39 +4287,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -4389,39 +4338,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
@@ -4433,39 +4382,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
@@ -4481,39 +4430,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -4525,39 +4474,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4572,39 +4521,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4616,39 +4565,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4660,39 +4609,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4704,39 +4653,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4748,39 +4697,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4792,39 +4741,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -4836,39 +4785,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -4880,39 +4829,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4924,39 +4873,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4968,39 +4917,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5019,39 +4968,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5063,39 +5012,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5107,39 +5056,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -5151,39 +5100,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5195,39 +5144,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5239,39 +5188,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -5283,39 +5232,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5327,39 +5276,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5378,39 +5327,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5422,40 +5371,40 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5474,39 +5423,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5518,39 +5467,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -5569,39 +5518,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -5633,39 +5582,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -5692,39 +5641,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -5736,39 +5685,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -5778,39 +5727,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -5820,39 +5769,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -5882,39 +5831,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -5932,39 +5881,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -5981,39 +5930,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6029,39 +5978,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -6090,39 +6039,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -6143,39 +6092,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6190,39 +6139,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -6236,40 +6185,40 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -6285,39 +6234,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -6333,39 +6282,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -6381,39 +6330,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -6429,40 +6378,40 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -6478,39 +6427,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6528,39 +6477,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -6576,39 +6525,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6623,39 +6572,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -6670,39 +6619,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -6723,40 +6672,40 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -6771,39 +6720,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -6824,104 +6773,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>尊敬的卖家：
-						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
-						每年 4-7 月欧美迎来学期末大促，紧接着7-10月进入返校季，在此期间学校批量采购教学设备，家庭为子女豪囤文具用品，企业为员工升级办公配置—— 千亿级市场需求在亚马逊集中爆发。根据亚马逊内部数据，相关ASIN转化率最高提升2.4倍。
-						为了帮助您把握这波商机，我们向您提前预告在这段时间内值得关注的选品方向，助您提前布局商品，做好库存准备。
-						哪些品类有机会爆发？
-						美国站
-						教室用品、书写工具及配件
-						纸张/笔记本、美术用品
-						家具、收纳与储物用品
-						笔记本电脑/平板/显示器
-						IT配件、餐饮服务用品
-						清洁用品与设备、玩具
-						欧洲站
-						办公用品、PC电脑
-						家居用品、家具
-						电子产品、厨房用品
-						商业/工业/科学用品
-						玩具、家居装修用品
-						以上仅为部分热门品类，您可结合店铺情况，重点关注与“教学办公、IT、家具与收纳、设施维护”相关的产品，点击下方文字了解具体商品推荐：
-						教学办公
-https://go.amazonsellerservices.com/e/229492/pageName-CN3AAS3AGS-B2B3Aintro/7z264nh/6566697502/h/Mt_Wi0H4RcCqjfEopZWckMJLYMWHT-V0a58wxKYZDFY
-						商用 IT
-https://go.amazonsellerservices.com/e/229492/pageName-CN3AAS3AGS-B2B3Aintro/7z264nl/6566697502/h/Mt_Wi0H4RcCqjfEopZWckMJLYMWHT-V0a58wxKYZDFY
-						家具与收纳
-https://go.amazonsellerservices.com/e/229492/pageName-CN3AAS3AGS-B2B3Aintro/7z264np/6566697502/h/Mt_Wi0H4RcCqjfEopZWckMJLYMWHT-V0a58wxKYZDFY
-						设施维护
-https://go.amazonsellerservices.com/e/229492/pageName-CN3AAS3AGS-B2B3Aintro/7z264ns/6566697502/h/Mt_Wi0H4RcCqjfEopZWckMJLYMWHT-V0a58wxKYZDFY
-						亚马逊店铺商品默认 C+B 双端同步可售，您的商品能够同时展现给个人消费者和</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -6934,39 +6818,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6987,39 +6871,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7042,39 +6926,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -7090,39 +6974,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -7142,39 +7026,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -7193,39 +7077,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -7234,39 +7118,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -7284,39 +7168,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -7346,39 +7230,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7394,39 +7278,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
